--- a/artfynd/A 52264-2022 artfynd.xlsx
+++ b/artfynd/A 52264-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52264-2022 artfynd.xlsx
+++ b/artfynd/A 52264-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104593637</v>
+        <v>104593620</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473780.3094452888</v>
+        <v>473808</v>
       </c>
       <c r="R2" t="n">
-        <v>7013777.427834951</v>
+        <v>7013974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104593632</v>
+        <v>104593621</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473815.7661137963</v>
+        <v>473766</v>
       </c>
       <c r="R3" t="n">
-        <v>7013977.153526685</v>
+        <v>7013701</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>104593622</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473830.905343441</v>
+        <v>473831</v>
       </c>
       <c r="R4" t="n">
-        <v>7013897.29666794</v>
+        <v>7013897</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1024,50 +979,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104593631</v>
+        <v>104593623</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vike, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473812.0075608135</v>
+        <v>473723</v>
       </c>
       <c r="R5" t="n">
-        <v>7013958.714830574</v>
+        <v>7013919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,19 +1055,14 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,15 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104593630</v>
+        <v>104593624</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473798.8866438381</v>
+        <v>473801</v>
       </c>
       <c r="R6" t="n">
-        <v>7013953.866335354</v>
+        <v>7013893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,19 +1157,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,15 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104593624</v>
+        <v>104593625</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473801.0947980214</v>
+        <v>473776</v>
       </c>
       <c r="R7" t="n">
-        <v>7013892.583679659</v>
+        <v>7013898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,19 +1254,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,37 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104593620</v>
+        <v>104593626</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473808.0725733605</v>
+        <v>473719</v>
       </c>
       <c r="R8" t="n">
-        <v>7013974.062789564</v>
+        <v>7013900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,19 +1351,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,37 +1380,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104593621</v>
+        <v>104593627</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473766.1571259646</v>
+        <v>473702</v>
       </c>
       <c r="R9" t="n">
-        <v>7013701.408301079</v>
+        <v>7013907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,19 +1448,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,58 +1477,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104593623</v>
+        <v>104593628</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vike, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473722.3678416939</v>
+        <v>473727</v>
       </c>
       <c r="R10" t="n">
-        <v>7013918.902128431</v>
+        <v>7013924</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,24 +1545,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,15 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104593627</v>
+        <v>104593629</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473701.5160585373</v>
+        <v>473761</v>
       </c>
       <c r="R11" t="n">
-        <v>7013906.458910029</v>
+        <v>7013952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,19 +1642,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,15 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104593628</v>
+        <v>104593630</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473726.4678040863</v>
+        <v>473799</v>
       </c>
       <c r="R12" t="n">
-        <v>7013923.823926651</v>
+        <v>7013954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,19 +1739,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,15 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104593626</v>
+        <v>104593631</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,10 +1803,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473718.6013391476</v>
+        <v>473812</v>
       </c>
       <c r="R13" t="n">
-        <v>7013899.562304306</v>
+        <v>7013959</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,19 +1836,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,15 +1865,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104593634</v>
+        <v>104593632</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473769.3477768434</v>
+        <v>473816</v>
       </c>
       <c r="R14" t="n">
-        <v>7013705.43688098</v>
+        <v>7013977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,19 +1933,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,15 +1962,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104593636</v>
+        <v>104593634</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +1997,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473782.4035598941</v>
+        <v>473769</v>
       </c>
       <c r="R15" t="n">
-        <v>7013757.588904253</v>
+        <v>7013706</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,19 +2030,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,15 +2059,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104593625</v>
+        <v>104593635</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,10 +2094,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473775.8828205758</v>
+        <v>473784</v>
       </c>
       <c r="R16" t="n">
-        <v>7013898.645042086</v>
+        <v>7013737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,19 +2127,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,15 +2156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104593629</v>
+        <v>104593636</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,10 +2191,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473760.983223469</v>
+        <v>473783</v>
       </c>
       <c r="R17" t="n">
-        <v>7013952.372943264</v>
+        <v>7013758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,19 +2224,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,15 +2253,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104593635</v>
+        <v>104593637</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,10 +2288,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473784.0392837755</v>
+        <v>473780</v>
       </c>
       <c r="R18" t="n">
-        <v>7013736.852580108</v>
+        <v>7013778</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,19 +2321,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 52264-2022 artfynd.xlsx
+++ b/artfynd/A 52264-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593620</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593621</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593622</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593623</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593624</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593625</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593626</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593627</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593628</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593629</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1765,6 +1820,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593630</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1862,6 +1922,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593631</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593632</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2056,6 +2126,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593634</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2153,6 +2228,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593635</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2250,6 +2330,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593636</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2347,8 +2432,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>